--- a/generation_zy/hiwo-物料2-1.xlsx
+++ b/generation_zy/hiwo-物料2-1.xlsx
@@ -2029,7 +2029,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>BENZANILIDE</t>
+          <t>试剂-12</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">

--- a/generation_zy/hiwo-物料2-1.xlsx
+++ b/generation_zy/hiwo-物料2-1.xlsx
@@ -2029,7 +2029,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>试剂-12</t>
+          <t>IS1</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
